--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117868871</v>
+        <v>117868872</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -811,24 +811,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Aspås Nv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471733</v>
+        <v>471670</v>
       </c>
       <c r="R3" t="n">
-        <v>7029407</v>
+        <v>7029572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117868872</v>
+        <v>117868871</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -921,16 +918,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aspås Nv, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471670</v>
+        <v>471733</v>
       </c>
       <c r="R4" t="n">
-        <v>7029572</v>
+        <v>7029407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117868874</v>
+        <v>117868871</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Aspås Nv, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471658</v>
+        <v>471733</v>
       </c>
       <c r="R2" t="n">
-        <v>7029770</v>
+        <v>7029407</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +788,7 @@
         <v>117868872</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117868871</v>
+        <v>117868874</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aspås Nv, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471733</v>
+        <v>471658</v>
       </c>
       <c r="R4" t="n">
-        <v>7029407</v>
+        <v>7029770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86205</v>
+        <v>86210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86210</v>
+        <v>86216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86216</v>
+        <v>86219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86219</v>
+        <v>86223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86223</v>
+        <v>86224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ljusblåa skivor och hela svampen reagerar positivt med KOH (förutom köttet), inkl myceltrådarna som blir rosa. Svampen har en behaglig doft. Funnen i blåbärsgranskog med få andra kalkindikatorer, mest svavelriskor och kransmossa. metarius bedöms vara mest troligt. Arten tycks delvis vara mer knuten till äldre barrskogar/naturskogar snarare än strikt kalkbarrskogar men detta är såklart en killgissning.</t>
+          <t>Ljusblåa skivor och hela svampen reagerar positivt med KOH (förutom köttet), inkl myceltrådarna som blir rosa. Svampen har en behaglig doft. Funnen i blåbärsgranskog med få andra kalkindikatorer, mest svavelriskor och kransmossa. metarius bedöms vara mest troligt. Arten tycks delvis vara mer knuten till äldre barrskogar/naturskogar snarare än strikt kalkbarrskogar men detta är såklart en teori.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86224</v>
+        <v>86231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,12 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86245</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1072,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ljusblåa skivor och hela svampen reagerar positivt med KOH (förutom köttet), inkl myceltrådarna som blir rosa. Svampen har en behaglig doft. Funnen i blåbärsgranskog med få andra kalkindikatorer, mest svavelriskor och kransmossa. metarius bedöms vara mest troligt. Arten tycks delvis vara mer knuten till äldre barrskogar/naturskogar snarare än strikt kalkbarrskogar men detta är såklart en teori.</t>
+          <t>Ljusblåa skivor och hela svampen reagerar positivt med KOH (förutom köttet), inkl myceltrådarna som blir rosa. Svampen har en behaglig doft. Funnen i blåbärsgranskog med få andra kalkindikatorer, mest svavelriskor och kransmossa. metarius bedöms vara mest troligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86870</v>
+        <v>86872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86872</v>
+        <v>86899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86899</v>
+        <v>86903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86903</v>
+        <v>86904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86904</v>
+        <v>86908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86908</v>
+        <v>86913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86920</v>
+        <v>86923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86923</v>
+        <v>86926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>119650885</v>
       </c>
       <c r="B5" t="n">
-        <v>86926</v>
+        <v>86930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11439-2024 artfynd.xlsx
+++ b/artfynd/A 11439-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117868871</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
